--- a/artfynd/A 31473-2023 artfynd.xlsx
+++ b/artfynd/A 31473-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31473-2023 artfynd.xlsx
+++ b/artfynd/A 31473-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112181727</v>
+        <v>81626</v>
       </c>
       <c r="B2" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rullbo, Dlr</t>
+          <t>Svartåns sydsida 1600 m VSV om Muslickbergets topp, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493005</v>
+        <v>493038</v>
       </c>
       <c r="R2" t="n">
-        <v>6845384</v>
+        <v>6845497</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
+          <t>2007-09-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
+          <t>2007-09-25</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>i flera träd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,31 +761,40 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>olikåldrig luckig barrblandskog med blåbär</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>torra grangrenar</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inv. av Hamra NP´s utvidgning, Lst X-län 2007</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>112182531</v>
       </c>
       <c r="B3" t="n">
-        <v>77441</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,12 +900,7 @@
         <v>112181635</v>
       </c>
       <c r="B4" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,37 +1003,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112182724</v>
+        <v>112181727</v>
       </c>
       <c r="B5" t="n">
-        <v>95746</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493165</v>
+        <v>493005</v>
       </c>
       <c r="R5" t="n">
-        <v>6845494</v>
+        <v>6845384</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1072,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1122,12 +1112,7 @@
         <v>112183278</v>
       </c>
       <c r="B6" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,7 +1151,7 @@
         <v>492536</v>
       </c>
       <c r="R6" t="n">
-        <v>6845328</v>
+        <v>6845329</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,6 +1212,112 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112182724</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rullbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>493166</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6845494</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31473-2023 artfynd.xlsx
+++ b/artfynd/A 31473-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182531</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112181635</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112181727</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183278</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
           <t>Inv. av Hamra NP´s utvidgning, Lst X-län 2007</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81626</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,8 +1348,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182724</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>